--- a/public/Excel_template/자재현황.xlsx
+++ b/public/Excel_template/자재현황.xlsx
@@ -5,22 +5,23 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ABC_product\product_manage\public\Excel_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47C0C9F-64AD-4FCA-B866-25258A517080}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{EC5CEFF0-25F6-4001-8E1A-CF497EB5CC6A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="12135" tabRatio="610" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="원시데이터 Rev.3" sheetId="89" r:id="rId1"/>
+    <sheet name="자재현황" sheetId="89" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'원시데이터 Rev.3'!$A$7:$Q$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'원시데이터 Rev.3'!$A$1:$Q$16</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'원시데이터 Rev.3'!$5:$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">자재현황!$A$7:$Q$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">자재현황!$A$1:$Q$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">자재현황!$5:$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -698,6 +699,81 @@
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -709,81 +785,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="31">
@@ -1217,46 +1218,46 @@
   <sheetData>
     <row r="1" spans="1:20" ht="8.1" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="42"/>
-      <c r="P2" s="42"/>
-      <c r="Q2" s="42"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
       <c r="R2" s="1"/>
       <c r="S2" s="2"/>
     </row>
     <row r="3" spans="1:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="42"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="42"/>
-      <c r="O3" s="42"/>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="42"/>
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
       <c r="R3" s="1"/>
       <c r="S3" s="2"/>
     </row>
@@ -1275,51 +1276,51 @@
       <c r="Q4" s="14"/>
     </row>
     <row r="5" spans="1:20" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="41" t="s">
+      <c r="D5" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="38" t="s">
+      <c r="E5" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="G5" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="38" t="s">
+      <c r="H5" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="35" t="s">
+      <c r="I5" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="29" t="s">
+      <c r="J5" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="32" t="s">
+      <c r="K5" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="L5" s="35" t="s">
+      <c r="L5" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="M5" s="50" t="s">
+      <c r="M5" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="N5" s="51"/>
-      <c r="O5" s="50" t="s">
+      <c r="N5" s="41"/>
+      <c r="O5" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="P5" s="51"/>
-      <c r="Q5" s="47" t="s">
+      <c r="P5" s="41"/>
+      <c r="Q5" s="37" t="s">
         <v>3</v>
       </c>
       <c r="R5" s="8"/>
@@ -1327,53 +1328,53 @@
       <c r="T5" s="10"/>
     </row>
     <row r="6" spans="1:20" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="45"/>
-      <c r="B6" s="33"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="23" t="s">
+      <c r="A6" s="29"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="N6" s="25" t="s">
+      <c r="N6" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="27" t="s">
+      <c r="O6" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="P6" s="25" t="s">
+      <c r="P6" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="Q6" s="48"/>
+      <c r="Q6" s="38"/>
       <c r="R6" s="8"/>
       <c r="S6" s="9"/>
       <c r="T6" s="10"/>
     </row>
     <row r="7" spans="1:20" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="46"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="28"/>
-      <c r="P7" s="26"/>
-      <c r="Q7" s="49"/>
+      <c r="A7" s="30"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="47"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="36"/>
+      <c r="M7" s="49"/>
+      <c r="N7" s="51"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="51"/>
+      <c r="Q7" s="39"/>
       <c r="R7" s="8"/>
       <c r="S7" s="8"/>
       <c r="T7" s="10"/>
@@ -1449,11 +1450,15 @@
     </row>
   </sheetData>
   <autoFilter ref="A7:Q9" xr:uid="{E9958AF1-1E2F-4E2C-A9EC-6D24381AE110}">
-    <sortState ref="A10:Q9">
+    <sortState ref="A9:Q10">
       <sortCondition ref="A7:A9"/>
     </sortState>
   </autoFilter>
   <mergeCells count="20">
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="P6:P7"/>
     <mergeCell ref="D5:D7"/>
     <mergeCell ref="A2:Q3"/>
     <mergeCell ref="A5:A7"/>
@@ -1470,10 +1475,6 @@
     <mergeCell ref="J5:J7"/>
     <mergeCell ref="K5:K7"/>
     <mergeCell ref="L5:L7"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="P6:P7"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>

--- a/public/Excel_template/자재현황.xlsx
+++ b/public/Excel_template/자재현황.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ABC_product\product_manage\public\Excel_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{EC5CEFF0-25F6-4001-8E1A-CF497EB5CC6A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7BD57DC-DC4A-42A6-BEDB-6A225C7A0614}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="12135" tabRatio="610" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,11 +17,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">자재현황!$A$7:$Q$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">자재현황!$A$1:$Q$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">자재현황!$5:$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -52,10 +50,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>GK사업소 전기기계</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>적정 재고 관리</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
@@ -117,6 +111,10 @@
   </si>
   <si>
     <t>2025년 자재 수불 대장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GK사업소</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -699,15 +697,21 @@
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -778,12 +782,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1218,52 +1216,52 @@
   <sheetData>
     <row r="1" spans="1:20" ht="8.1" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
+      <c r="A2" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
       <c r="R2" s="1"/>
       <c r="S2" s="2"/>
     </row>
     <row r="3" spans="1:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="26"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="28"/>
       <c r="R3" s="1"/>
       <c r="S3" s="2"/>
     </row>
     <row r="4" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C4" s="6"/>
       <c r="H4" s="13"/>
@@ -1276,51 +1274,51 @@
       <c r="Q4" s="14"/>
     </row>
     <row r="5" spans="1:20" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="C5" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="D5" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="42" t="s">
+      <c r="F5" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="G5" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="H5" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="42" t="s">
+      <c r="I5" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="34" t="s">
+      <c r="J5" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="45" t="s">
+      <c r="K5" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" s="34" t="s">
+      <c r="L5" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="M5" s="40" t="s">
+      <c r="M5" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="N5" s="41"/>
-      <c r="O5" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="P5" s="41"/>
-      <c r="Q5" s="37" t="s">
+      <c r="N5" s="43"/>
+      <c r="O5" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="P5" s="43"/>
+      <c r="Q5" s="39" t="s">
         <v>3</v>
       </c>
       <c r="R5" s="8"/>
@@ -1328,53 +1326,53 @@
       <c r="T5" s="10"/>
     </row>
     <row r="6" spans="1:20" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="29"/>
-      <c r="B6" s="32"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="32"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="48" t="s">
+      <c r="A6" s="31"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="37"/>
+      <c r="M6" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="N6" s="50" t="s">
+      <c r="N6" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="24" t="s">
+      <c r="O6" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="P6" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="P6" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q6" s="38"/>
+      <c r="Q6" s="40"/>
       <c r="R6" s="8"/>
       <c r="S6" s="9"/>
       <c r="T6" s="10"/>
     </row>
     <row r="7" spans="1:20" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="30"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="47"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="49"/>
-      <c r="N7" s="51"/>
-      <c r="O7" s="25"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="39"/>
+      <c r="A7" s="32"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="51"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="41"/>
       <c r="R7" s="8"/>
       <c r="S7" s="8"/>
       <c r="T7" s="10"/>
@@ -1439,7 +1437,7 @@
       <c r="N10" s="16"/>
       <c r="O10" s="16"/>
       <c r="P10" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q10" s="15"/>
     </row>
@@ -1455,6 +1453,9 @@
     </sortState>
   </autoFilter>
   <mergeCells count="20">
+    <mergeCell ref="J5:J7"/>
+    <mergeCell ref="K5:K7"/>
+    <mergeCell ref="L5:L7"/>
     <mergeCell ref="M6:M7"/>
     <mergeCell ref="N6:N7"/>
     <mergeCell ref="O6:O7"/>
@@ -1472,9 +1473,6 @@
     <mergeCell ref="F5:F7"/>
     <mergeCell ref="G5:G7"/>
     <mergeCell ref="H5:H7"/>
-    <mergeCell ref="J5:J7"/>
-    <mergeCell ref="K5:K7"/>
-    <mergeCell ref="L5:L7"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
